--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/52.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/52.xlsx
@@ -426,13 +426,13 @@
         <v>-9.386994427324552</v>
       </c>
       <c r="E2">
-        <v>-13.93618158245679</v>
+        <v>-21.62659916734687</v>
       </c>
       <c r="F2">
-        <v>-5.178780020762832</v>
+        <v>-4.96909455172479</v>
       </c>
       <c r="G2">
-        <v>-9.90867913516705</v>
+        <v>-14.07029144531023</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.407183920347096</v>
       </c>
       <c r="E3">
-        <v>-15.48545858148696</v>
+        <v>-22.26858734199227</v>
       </c>
       <c r="F3">
-        <v>-4.61347559733556</v>
+        <v>-4.973301829763609</v>
       </c>
       <c r="G3">
-        <v>-11.35538091473748</v>
+        <v>-12.93045240813869</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.382926508040988</v>
       </c>
       <c r="E4">
-        <v>-14.53837352752279</v>
+        <v>-21.08949045071911</v>
       </c>
       <c r="F4">
-        <v>-4.850977643759609</v>
+        <v>-5.424540061825389</v>
       </c>
       <c r="G4">
-        <v>-11.41701996213317</v>
+        <v>-12.788307514319</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.3056080157026</v>
       </c>
       <c r="E5">
-        <v>-15.59526954769896</v>
+        <v>-23.75306640644669</v>
       </c>
       <c r="F5">
-        <v>-4.601562845715899</v>
+        <v>-4.815772857508033</v>
       </c>
       <c r="G5">
-        <v>-10.44304091175189</v>
+        <v>-13.08711404414808</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.171229644580427</v>
       </c>
       <c r="E6">
-        <v>-15.75313668008036</v>
+        <v>-23.75772620620058</v>
       </c>
       <c r="F6">
-        <v>-4.694769089144095</v>
+        <v>-5.061460002239143</v>
       </c>
       <c r="G6">
-        <v>-10.36880192803373</v>
+        <v>-13.56530248402257</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.973216465089413</v>
       </c>
       <c r="E7">
-        <v>-15.79216759755247</v>
+        <v>-23.58602005725174</v>
       </c>
       <c r="F7">
-        <v>-4.862066998180886</v>
+        <v>-4.40549822188209</v>
       </c>
       <c r="G7">
-        <v>-11.2765204094465</v>
+        <v>-13.25914323255077</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.713324150503595</v>
       </c>
       <c r="E8">
-        <v>-15.97947886793174</v>
+        <v>-25.20106408429532</v>
       </c>
       <c r="F8">
-        <v>-4.179819463398199</v>
+        <v>-4.287416933715229</v>
       </c>
       <c r="G8">
-        <v>-10.29134509405141</v>
+        <v>-13.33400459883031</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.394658922075912</v>
       </c>
       <c r="E9">
-        <v>-16.11545082848605</v>
+        <v>-23.76828207911246</v>
       </c>
       <c r="F9">
-        <v>-4.268336318959146</v>
+        <v>-5.069445464002131</v>
       </c>
       <c r="G9">
-        <v>-10.77235742927089</v>
+        <v>-12.8503769326348</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.020023788158804</v>
       </c>
       <c r="E10">
-        <v>-17.33960603613553</v>
+        <v>-26.11248287697508</v>
       </c>
       <c r="F10">
-        <v>-4.082882253187795</v>
+        <v>-4.697592165252836</v>
       </c>
       <c r="G10">
-        <v>-11.76622954779765</v>
+        <v>-14.05712540570054</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.598075149240985</v>
       </c>
       <c r="E11">
-        <v>-17.16236156347531</v>
+        <v>-22.47668883654075</v>
       </c>
       <c r="F11">
-        <v>-3.907920288940303</v>
+        <v>-4.492178586911031</v>
       </c>
       <c r="G11">
-        <v>-10.24416319902571</v>
+        <v>-14.84330382873005</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.139363245636726</v>
       </c>
       <c r="E12">
-        <v>-18.23392531096233</v>
+        <v>-25.1191077617045</v>
       </c>
       <c r="F12">
-        <v>-3.749984588289952</v>
+        <v>-3.82319487098197</v>
       </c>
       <c r="G12">
-        <v>-10.20039778699655</v>
+        <v>-14.31366123481144</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.653751822556973</v>
       </c>
       <c r="E13">
-        <v>-18.0319915980123</v>
+        <v>-24.14246988636626</v>
       </c>
       <c r="F13">
-        <v>-3.810259085619852</v>
+        <v>-4.63395780973718</v>
       </c>
       <c r="G13">
-        <v>-8.849066203321442</v>
+        <v>-13.57462498026116</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.162074225743332</v>
       </c>
       <c r="E14">
-        <v>-19.70419402398068</v>
+        <v>-25.30839344675111</v>
       </c>
       <c r="F14">
-        <v>-3.248658292850497</v>
+        <v>-3.416049807403804</v>
       </c>
       <c r="G14">
-        <v>-10.27751032424279</v>
+        <v>-13.42642840919568</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.679905388998604</v>
       </c>
       <c r="E15">
-        <v>-19.88742966775305</v>
+        <v>-25.86146956272992</v>
       </c>
       <c r="F15">
-        <v>-3.428960741743837</v>
+        <v>-3.310147176792901</v>
       </c>
       <c r="G15">
-        <v>-9.973910124472848</v>
+        <v>-14.33072709706638</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.223657087912176</v>
       </c>
       <c r="E16">
-        <v>-20.31396210606151</v>
+        <v>-25.86610219163976</v>
       </c>
       <c r="F16">
-        <v>-2.996478404416243</v>
+        <v>-3.19344180688209</v>
       </c>
       <c r="G16">
-        <v>-8.795700209228391</v>
+        <v>-11.90242539128327</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.811279207593428</v>
       </c>
       <c r="E17">
-        <v>-19.11674226180966</v>
+        <v>-27.61259423370398</v>
       </c>
       <c r="F17">
-        <v>-2.719064788157911</v>
+        <v>-2.855496071031587</v>
       </c>
       <c r="G17">
-        <v>-8.784642987127224</v>
+        <v>-11.78679796723314</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.458283272106252</v>
       </c>
       <c r="E18">
-        <v>-21.78971027262914</v>
+        <v>-26.86533262380227</v>
       </c>
       <c r="F18">
-        <v>-2.304309513250227</v>
+        <v>-2.85303499147787</v>
       </c>
       <c r="G18">
-        <v>-8.831659354875955</v>
+        <v>-12.73453432312462</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.178372381550214</v>
       </c>
       <c r="E19">
-        <v>-20.22741843930093</v>
+        <v>-27.17257147132667</v>
       </c>
       <c r="F19">
-        <v>-2.783206932891483</v>
+        <v>-2.932187981917571</v>
       </c>
       <c r="G19">
-        <v>-8.080920321844349</v>
+        <v>-11.67372959488488</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.983816657266904</v>
       </c>
       <c r="E20">
-        <v>-21.07068822663926</v>
+        <v>-28.0954835310379</v>
       </c>
       <c r="F20">
-        <v>-2.064831810570501</v>
+        <v>-2.467634572223191</v>
       </c>
       <c r="G20">
-        <v>-8.547823111975461</v>
+        <v>-13.58261332664742</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.875995626308327</v>
       </c>
       <c r="E21">
-        <v>-21.4514513781522</v>
+        <v>-27.97099578056704</v>
       </c>
       <c r="F21">
-        <v>-1.574106961152074</v>
+        <v>-2.525858860231163</v>
       </c>
       <c r="G21">
-        <v>-8.728588830056285</v>
+        <v>-12.5193157576166</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.857335458447288</v>
       </c>
       <c r="E22">
-        <v>-22.29861112466313</v>
+        <v>-27.76375922455403</v>
       </c>
       <c r="F22">
-        <v>-1.99492257197864</v>
+        <v>-2.470725211003036</v>
       </c>
       <c r="G22">
-        <v>-8.880628944492853</v>
+        <v>-12.79113803075508</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.92522283995241</v>
       </c>
       <c r="E23">
-        <v>-22.23000474344692</v>
+        <v>-29.18006211282297</v>
       </c>
       <c r="F23">
-        <v>-1.609346538834568</v>
+        <v>-2.101912020622015</v>
       </c>
       <c r="G23">
-        <v>-9.039409329647379</v>
+        <v>-11.31113878415066</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.072038144194229</v>
       </c>
       <c r="E24">
-        <v>-21.38635003581793</v>
+        <v>-28.21616736334232</v>
       </c>
       <c r="F24">
-        <v>-2.035392461442409</v>
+        <v>-2.015462770098456</v>
       </c>
       <c r="G24">
-        <v>-8.291030715585272</v>
+        <v>-11.46356292186978</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.29225028557985</v>
       </c>
       <c r="E25">
-        <v>-22.4046317581307</v>
+        <v>-31.26937548692686</v>
       </c>
       <c r="F25">
-        <v>-1.99403787559245</v>
+        <v>-2.006310138664924</v>
       </c>
       <c r="G25">
-        <v>-8.323450888051356</v>
+        <v>-11.28925276759054</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.57330519496024</v>
       </c>
       <c r="E26">
-        <v>-21.54711086309023</v>
+        <v>-30.98348160163761</v>
       </c>
       <c r="F26">
-        <v>-2.106635371552778</v>
+        <v>-1.837920441391244</v>
       </c>
       <c r="G26">
-        <v>-8.365839113136184</v>
+        <v>-11.33415700728521</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.898254448764346</v>
       </c>
       <c r="E27">
-        <v>-22.54170413786888</v>
+        <v>-30.05004536833255</v>
       </c>
       <c r="F27">
-        <v>-1.477606300562945</v>
+        <v>-2.16219065978893</v>
       </c>
       <c r="G27">
-        <v>-7.867476208745378</v>
+        <v>-12.68393925564794</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.252927340127469</v>
       </c>
       <c r="E28">
-        <v>-22.40213656895248</v>
+        <v>-29.14215878537877</v>
       </c>
       <c r="F28">
-        <v>-1.625146818675566</v>
+        <v>-1.458704613165866</v>
       </c>
       <c r="G28">
-        <v>-8.700038685325611</v>
+        <v>-13.00293018162995</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.620740710822097</v>
       </c>
       <c r="E29">
-        <v>-22.4842740305036</v>
+        <v>-28.67935779874287</v>
       </c>
       <c r="F29">
-        <v>-1.914419342672375</v>
+        <v>-2.530556531772439</v>
       </c>
       <c r="G29">
-        <v>-9.572354192741411</v>
+        <v>-12.45948757863089</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.985630936070229</v>
       </c>
       <c r="E30">
-        <v>-20.94228334615177</v>
+        <v>-28.5261097098493</v>
       </c>
       <c r="F30">
-        <v>-1.673744649095604</v>
+        <v>-2.191645747897675</v>
       </c>
       <c r="G30">
-        <v>-8.304954870123447</v>
+        <v>-13.64289339509924</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.336072394141529</v>
       </c>
       <c r="E31">
-        <v>-21.40520207311186</v>
+        <v>-28.54243938712096</v>
       </c>
       <c r="F31">
-        <v>-2.17261814865537</v>
+        <v>-2.450396246570934</v>
       </c>
       <c r="G31">
-        <v>-9.687951821881683</v>
+        <v>-12.08466099158353</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.657680825482059</v>
       </c>
       <c r="E32">
-        <v>-21.10519972705172</v>
+        <v>-26.41466794750693</v>
       </c>
       <c r="F32">
-        <v>-1.82158586457544</v>
+        <v>-2.510862925138284</v>
       </c>
       <c r="G32">
-        <v>-8.986506811929825</v>
+        <v>-12.89840963786408</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.94258089302198</v>
       </c>
       <c r="E33">
-        <v>-20.6439791778445</v>
+        <v>-27.63163193843223</v>
       </c>
       <c r="F33">
-        <v>-2.058020145417281</v>
+        <v>-1.537312537854525</v>
       </c>
       <c r="G33">
-        <v>-9.358201622897036</v>
+        <v>-12.71252912692509</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.186532767985478</v>
       </c>
       <c r="E34">
-        <v>-19.96711269639202</v>
+        <v>-27.01086872146078</v>
       </c>
       <c r="F34">
-        <v>-2.206150461120694</v>
+        <v>-2.577629337803924</v>
       </c>
       <c r="G34">
-        <v>-9.729965955320573</v>
+        <v>-12.95416253529095</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.386432666913892</v>
       </c>
       <c r="E35">
-        <v>-18.05811183608854</v>
+        <v>-27.84461965643499</v>
       </c>
       <c r="F35">
-        <v>-2.564741597751169</v>
+        <v>-2.06506541017809</v>
       </c>
       <c r="G35">
-        <v>-8.508205813507002</v>
+        <v>-12.62713691528512</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.544400469360849</v>
       </c>
       <c r="E36">
-        <v>-19.54175313285154</v>
+        <v>-27.04708745657412</v>
       </c>
       <c r="F36">
-        <v>-2.450745817614915</v>
+        <v>-2.545108461937418</v>
       </c>
       <c r="G36">
-        <v>-8.995329415791982</v>
+        <v>-12.46948542615949</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.665443903858223</v>
       </c>
       <c r="E37">
-        <v>-21.0855280359624</v>
+        <v>-26.18643738599435</v>
       </c>
       <c r="F37">
-        <v>-1.960208179229521</v>
+        <v>-2.490683895206088</v>
       </c>
       <c r="G37">
-        <v>-8.968547102379278</v>
+        <v>-12.66794269960218</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.752303582107924</v>
       </c>
       <c r="E38">
-        <v>-19.22242778820067</v>
+        <v>-26.38633328564093</v>
       </c>
       <c r="F38">
-        <v>-2.003501144802031</v>
+        <v>-2.451123553150591</v>
       </c>
       <c r="G38">
-        <v>-9.136623499408076</v>
+        <v>-11.95380174750722</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.817123858819619</v>
       </c>
       <c r="E39">
-        <v>-16.91359437233795</v>
+        <v>-26.03399989394815</v>
       </c>
       <c r="F39">
-        <v>-2.041202630405645</v>
+        <v>-2.531264785901833</v>
       </c>
       <c r="G39">
-        <v>-9.131545122550834</v>
+        <v>-11.88660760469663</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.870389946851229</v>
       </c>
       <c r="E40">
-        <v>-18.73761841788749</v>
+        <v>-23.87547558734803</v>
       </c>
       <c r="F40">
-        <v>-1.959571993064171</v>
+        <v>-2.728260494696389</v>
       </c>
       <c r="G40">
-        <v>-9.085197485001038</v>
+        <v>-11.20322824175258</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.920588864559578</v>
       </c>
       <c r="E41">
-        <v>-18.57458882513735</v>
+        <v>-25.30440386115036</v>
       </c>
       <c r="F41">
-        <v>-1.99818054097385</v>
+        <v>-2.640138770386577</v>
       </c>
       <c r="G41">
-        <v>-9.077450808439144</v>
+        <v>-12.84940032170071</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.981578377626414</v>
       </c>
       <c r="E42">
-        <v>-17.73258248204716</v>
+        <v>-24.86842502606189</v>
       </c>
       <c r="F42">
-        <v>-2.055955853849504</v>
+        <v>-2.627640363013138</v>
       </c>
       <c r="G42">
-        <v>-9.073805897800407</v>
+        <v>-12.18751964148868</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.059877488353253</v>
       </c>
       <c r="E43">
-        <v>-17.83128962999235</v>
+        <v>-24.48929212519171</v>
       </c>
       <c r="F43">
-        <v>-2.165575368996768</v>
+        <v>-3.310769280712404</v>
       </c>
       <c r="G43">
-        <v>-8.585563331123153</v>
+        <v>-12.24155767632621</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.160831472210234</v>
       </c>
       <c r="E44">
-        <v>-16.78686502723329</v>
+        <v>-24.84545660589499</v>
       </c>
       <c r="F44">
-        <v>-2.30358552014018</v>
+        <v>-2.736778596699376</v>
       </c>
       <c r="G44">
-        <v>-9.764190375105558</v>
+        <v>-11.85977563310084</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.29166386509911</v>
       </c>
       <c r="E45">
-        <v>-17.74311118411499</v>
+        <v>-24.30725199855737</v>
       </c>
       <c r="F45">
-        <v>-2.070154899500891</v>
+        <v>-3.279023756734918</v>
       </c>
       <c r="G45">
-        <v>-7.00636689798001</v>
+        <v>-11.38913854760143</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.454382366954372</v>
       </c>
       <c r="E46">
-        <v>-16.88798132335057</v>
+        <v>-23.47580605685306</v>
       </c>
       <c r="F46">
-        <v>-2.224614770529095</v>
+        <v>-3.345360246718506</v>
       </c>
       <c r="G46">
-        <v>-8.322186259655354</v>
+        <v>-11.28857410575499</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.649595432359492</v>
       </c>
       <c r="E47">
-        <v>-16.70508078665477</v>
+        <v>-24.89934997506027</v>
       </c>
       <c r="F47">
-        <v>-2.340090843214151</v>
+        <v>-3.019474711885361</v>
       </c>
       <c r="G47">
-        <v>-8.439425919383105</v>
+        <v>-12.25099935220421</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.878050757671623</v>
       </c>
       <c r="E48">
-        <v>-15.76772742333307</v>
+        <v>-24.73822686986736</v>
       </c>
       <c r="F48">
-        <v>-2.218408641947321</v>
+        <v>-3.395266897634968</v>
       </c>
       <c r="G48">
-        <v>-8.616904265743432</v>
+        <v>-11.23867425284155</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.128826548723135</v>
       </c>
       <c r="E49">
-        <v>-16.39726229445738</v>
+        <v>-23.33574035579582</v>
       </c>
       <c r="F49">
-        <v>-2.564078075461527</v>
+        <v>-3.1300634168939</v>
       </c>
       <c r="G49">
-        <v>-8.778286739691824</v>
+        <v>-13.32036846175405</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.397021529130667</v>
       </c>
       <c r="E50">
-        <v>-15.54544727666657</v>
+        <v>-24.57464933176229</v>
       </c>
       <c r="F50">
-        <v>-2.972195642370579</v>
+        <v>-3.332645635452936</v>
       </c>
       <c r="G50">
-        <v>-8.402751695899058</v>
+        <v>-12.56080020376921</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.674072962238268</v>
       </c>
       <c r="E51">
-        <v>-16.392901373988</v>
+        <v>-22.38456156132871</v>
       </c>
       <c r="F51">
-        <v>-2.872046851739521</v>
+        <v>-3.595304371532603</v>
       </c>
       <c r="G51">
-        <v>-9.194812958351847</v>
+        <v>-11.30619945020607</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.947622056049005</v>
       </c>
       <c r="E52">
-        <v>-16.95893345410274</v>
+        <v>-24.56364061144965</v>
       </c>
       <c r="F52">
-        <v>-2.87128309699414</v>
+        <v>-3.557460406735708</v>
       </c>
       <c r="G52">
-        <v>-8.220373742140607</v>
+        <v>-11.45195945975464</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.21036073655945</v>
       </c>
       <c r="E53">
-        <v>-15.50992592655041</v>
+        <v>-22.68672851796452</v>
       </c>
       <c r="F53">
-        <v>-2.896734685445155</v>
+        <v>-3.532656601593682</v>
       </c>
       <c r="G53">
-        <v>-8.761214256345802</v>
+        <v>-11.46407274588283</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.45179102848763</v>
       </c>
       <c r="E54">
-        <v>-16.36723851178653</v>
+        <v>-24.64433348979232</v>
       </c>
       <c r="F54">
-        <v>-3.056288187633173</v>
+        <v>-4.331906061817382</v>
       </c>
       <c r="G54">
-        <v>-9.30581555028361</v>
+        <v>-11.89137810081872</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.65915333089926</v>
       </c>
       <c r="E55">
-        <v>-15.75054639294797</v>
+        <v>-22.4793108229912</v>
       </c>
       <c r="F55">
-        <v>-3.367093293898353</v>
+        <v>-4.298036603819119</v>
       </c>
       <c r="G55">
-        <v>-10.22676959276238</v>
+        <v>-12.34712435248249</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.82826702201077</v>
       </c>
       <c r="E56">
-        <v>-15.73785760877848</v>
+        <v>-21.83104165489715</v>
       </c>
       <c r="F56">
-        <v>-3.030971623068815</v>
+        <v>-4.078879581897468</v>
       </c>
       <c r="G56">
-        <v>-9.136504319768664</v>
+        <v>-12.72371214975674</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.95374921046438</v>
       </c>
       <c r="E57">
-        <v>-17.02468689669412</v>
+        <v>-21.95729098175699</v>
       </c>
       <c r="F57">
-        <v>-2.928114899398006</v>
+        <v>-3.896763836759399</v>
       </c>
       <c r="G57">
-        <v>-9.426945101020003</v>
+        <v>-11.41905925818536</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.03074642022721</v>
       </c>
       <c r="E58">
-        <v>-16.44288667008466</v>
+        <v>-23.01617047354853</v>
       </c>
       <c r="F58">
-        <v>-2.872385654007266</v>
+        <v>-3.009848254297427</v>
       </c>
       <c r="G58">
-        <v>-8.763776618593198</v>
+        <v>-12.46555249805884</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.06303203513398</v>
       </c>
       <c r="E59">
-        <v>-16.42727702018022</v>
+        <v>-22.65552280357766</v>
       </c>
       <c r="F59">
-        <v>-3.182818823308589</v>
+        <v>-3.851243391240761</v>
       </c>
       <c r="G59">
-        <v>-9.668303734106107</v>
+        <v>-12.38890012664255</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.04831797778228</v>
       </c>
       <c r="E60">
-        <v>-16.57179873966101</v>
+        <v>-22.24956775116005</v>
       </c>
       <c r="F60">
-        <v>-3.600311852482526</v>
+        <v>-4.284186300844311</v>
       </c>
       <c r="G60">
-        <v>-9.50172370366106</v>
+        <v>-12.66448317951364</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.98981922073443</v>
       </c>
       <c r="E61">
-        <v>-15.75903275323835</v>
+        <v>-23.80965421764654</v>
       </c>
       <c r="F61">
-        <v>-3.581528621624047</v>
+        <v>-3.363585157947497</v>
       </c>
       <c r="G61">
-        <v>-9.53379295829998</v>
+        <v>-13.31729627549361</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.8942894038523</v>
       </c>
       <c r="E62">
-        <v>-15.95758369610465</v>
+        <v>-23.99100148775771</v>
       </c>
       <c r="F62">
-        <v>-3.34273680715384</v>
+        <v>-3.987476694305168</v>
       </c>
       <c r="G62">
-        <v>-9.561449255735052</v>
+        <v>-13.03251321656888</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.76665659814509</v>
       </c>
       <c r="E63">
-        <v>-16.77656727733985</v>
+        <v>-22.83375901204556</v>
       </c>
       <c r="F63">
-        <v>-3.222153849430524</v>
+        <v>-4.253237666308319</v>
       </c>
       <c r="G63">
-        <v>-9.627243037782527</v>
+        <v>-12.02734882720767</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.61662808034795</v>
       </c>
       <c r="E64">
-        <v>-16.22096427286477</v>
+        <v>-24.07115547769347</v>
       </c>
       <c r="F64">
-        <v>-3.469988950837094</v>
+        <v>-4.061666935634697</v>
       </c>
       <c r="G64">
-        <v>-8.841514848946364</v>
+        <v>-11.8604973320284</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.4553824665235</v>
       </c>
       <c r="E65">
-        <v>-16.78361358289579</v>
+        <v>-23.8445823376677</v>
       </c>
       <c r="F65">
-        <v>-3.803618892519012</v>
+        <v>-3.903226759236041</v>
       </c>
       <c r="G65">
-        <v>-8.83381120947648</v>
+        <v>-13.19585884402206</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.28575468520442</v>
       </c>
       <c r="E66">
-        <v>-16.03242125755541</v>
+        <v>-24.369609085643</v>
       </c>
       <c r="F66">
-        <v>-3.619147270487381</v>
+        <v>-4.253521796327479</v>
       </c>
       <c r="G66">
-        <v>-8.981186765248216</v>
+        <v>-13.58439605542031</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.11837043381714</v>
       </c>
       <c r="E67">
-        <v>-17.31226311007722</v>
+        <v>-23.47903485882053</v>
       </c>
       <c r="F67">
-        <v>-3.307168367612434</v>
+        <v>-4.028028592141815</v>
       </c>
       <c r="G67">
-        <v>-9.943459726602633</v>
+        <v>-12.66226180345679</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.959479088788047</v>
       </c>
       <c r="E68">
-        <v>-15.83948109398461</v>
+        <v>-24.43941551247123</v>
       </c>
       <c r="F68">
-        <v>-3.521901907603136</v>
+        <v>-4.424816578082778</v>
       </c>
       <c r="G68">
-        <v>-9.87896698895209</v>
+        <v>-12.21986367140737</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.810157055267101</v>
       </c>
       <c r="E69">
-        <v>-17.33536285599034</v>
+        <v>-23.15864079430385</v>
       </c>
       <c r="F69">
-        <v>-3.969667623512381</v>
+        <v>-3.967993492991323</v>
       </c>
       <c r="G69">
-        <v>-9.533382450653111</v>
+        <v>-13.85185999535634</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.679095048705522</v>
       </c>
       <c r="E70">
-        <v>-16.26126316305903</v>
+        <v>-26.2748467840461</v>
       </c>
       <c r="F70">
-        <v>-3.587067086079165</v>
+        <v>-4.434604567314257</v>
       </c>
       <c r="G70">
-        <v>-8.694467037183017</v>
+        <v>-12.83095065141035</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.566144876644397</v>
       </c>
       <c r="E71">
-        <v>-16.7242860449213</v>
+        <v>-26.69211396453487</v>
       </c>
       <c r="F71">
-        <v>-3.433717227370712</v>
+        <v>-4.051966753347915</v>
       </c>
       <c r="G71">
-        <v>-9.17221848504632</v>
+        <v>-12.94609804635729</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.469051267360294</v>
       </c>
       <c r="E72">
-        <v>-16.28010614340494</v>
+        <v>-25.34523258280351</v>
       </c>
       <c r="F72">
-        <v>-3.224587592859949</v>
+        <v>-4.201726467732635</v>
       </c>
       <c r="G72">
-        <v>-9.55259685696304</v>
+        <v>-12.58298416942786</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.388309534320292</v>
       </c>
       <c r="E73">
-        <v>-16.44924464759143</v>
+        <v>-25.34175471476562</v>
       </c>
       <c r="F73">
-        <v>-3.615663157191207</v>
+        <v>-3.481546332840953</v>
       </c>
       <c r="G73">
-        <v>-8.258911802763263</v>
+        <v>-12.76145898999551</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.320280471577647</v>
       </c>
       <c r="E74">
-        <v>-16.26881212922981</v>
+        <v>-25.15784885684012</v>
       </c>
       <c r="F74">
-        <v>-3.651810625547169</v>
+        <v>-3.937068881110012</v>
       </c>
       <c r="G74">
-        <v>-8.697257827072622</v>
+        <v>-12.76666647812879</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.261118697320191</v>
       </c>
       <c r="E75">
-        <v>-17.18732251220559</v>
+        <v>-25.71666707786065</v>
       </c>
       <c r="F75">
-        <v>-3.569378128559784</v>
+        <v>-4.352215145431818</v>
       </c>
       <c r="G75">
-        <v>-8.743002945334272</v>
+        <v>-12.05512761482769</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.211260803166423</v>
       </c>
       <c r="E76">
-        <v>-18.51054261724687</v>
+        <v>-24.11552999449463</v>
       </c>
       <c r="F76">
-        <v>-3.950730316316982</v>
+        <v>-4.570370671163484</v>
       </c>
       <c r="G76">
-        <v>-8.084009060832489</v>
+        <v>-12.20984596060553</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.16219012513886</v>
       </c>
       <c r="E77">
-        <v>-18.69211631105842</v>
+        <v>-26.49162483479328</v>
       </c>
       <c r="F77">
-        <v>-3.793327255906631</v>
+        <v>-5.240142164492608</v>
       </c>
       <c r="G77">
-        <v>-7.408075114806254</v>
+        <v>-11.95487767480748</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.111107560812261</v>
       </c>
       <c r="E78">
-        <v>-18.50732740070142</v>
+        <v>-25.42704852270009</v>
       </c>
       <c r="F78">
-        <v>-3.791808858457299</v>
+        <v>-4.803576804236616</v>
       </c>
       <c r="G78">
-        <v>-9.134613998265738</v>
+        <v>-11.01504359111824</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.055433614002478</v>
       </c>
       <c r="E79">
-        <v>-18.05038173095745</v>
+        <v>-25.08452380570792</v>
       </c>
       <c r="F79">
-        <v>-3.919653284833555</v>
+        <v>-5.063763691986328</v>
       </c>
       <c r="G79">
-        <v>-8.30898380404474</v>
+        <v>-11.68886209854488</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.990398727721209</v>
       </c>
       <c r="E80">
-        <v>-19.07590448320848</v>
+        <v>-26.71532239382418</v>
       </c>
       <c r="F80">
-        <v>-4.09761642418139</v>
+        <v>-3.966024463674869</v>
       </c>
       <c r="G80">
-        <v>-9.214785479590269</v>
+        <v>-11.96467026851264</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.918196050234098</v>
       </c>
       <c r="E81">
-        <v>-19.09871893525913</v>
+        <v>-27.25322812187729</v>
       </c>
       <c r="F81">
-        <v>-4.423304807572668</v>
+        <v>-4.596114673307688</v>
       </c>
       <c r="G81">
-        <v>-8.850234825896806</v>
+        <v>-11.13022078097503</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.839475491025247</v>
       </c>
       <c r="E82">
-        <v>-20.12144761904743</v>
+        <v>-26.82298233488253</v>
       </c>
       <c r="F82">
-        <v>-3.762106088495117</v>
+        <v>-4.216687611394597</v>
       </c>
       <c r="G82">
-        <v>-8.722590121539126</v>
+        <v>-12.76795096979802</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.751249816860286</v>
       </c>
       <c r="E83">
-        <v>-20.4982709981737</v>
+        <v>-29.00904882039731</v>
       </c>
       <c r="F83">
-        <v>-4.231097890733697</v>
+        <v>-4.498790615520177</v>
       </c>
       <c r="G83">
-        <v>-8.582944689601588</v>
+        <v>-12.26386744271536</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.657199640456835</v>
       </c>
       <c r="E84">
-        <v>-21.28628434567044</v>
+        <v>-28.60110576789033</v>
       </c>
       <c r="F84">
-        <v>-3.996196917954438</v>
+        <v>-4.998798978421777</v>
       </c>
       <c r="G84">
-        <v>-8.145697766411267</v>
+        <v>-12.15561922467227</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.558806814539894</v>
       </c>
       <c r="E85">
-        <v>-20.53486106815567</v>
+        <v>-30.86954066713062</v>
       </c>
       <c r="F85">
-        <v>-4.461624255258771</v>
+        <v>-4.878655883789349</v>
       </c>
       <c r="G85">
-        <v>-9.125582830034608</v>
+        <v>-12.44463647134172</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.455461098008342</v>
       </c>
       <c r="E86">
-        <v>-21.84824532765229</v>
+        <v>-29.27425437218251</v>
       </c>
       <c r="F86">
-        <v>-4.52027101064217</v>
+        <v>-4.873145583825926</v>
       </c>
       <c r="G86">
-        <v>-8.205151853751039</v>
+        <v>-11.67674550187115</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.354198635352382</v>
       </c>
       <c r="E87">
-        <v>-22.9317868888896</v>
+        <v>-31.33624746259813</v>
       </c>
       <c r="F87">
-        <v>-4.131161162157756</v>
+        <v>-4.675831781948695</v>
       </c>
       <c r="G87">
-        <v>-8.540841171433138</v>
+        <v>-12.83085133504418</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.253427373124493</v>
       </c>
       <c r="E88">
-        <v>-24.51632711501751</v>
+        <v>-32.5415642183757</v>
       </c>
       <c r="F88">
-        <v>-4.494899773829227</v>
+        <v>-5.45729619403429</v>
       </c>
       <c r="G88">
-        <v>-8.636535800791311</v>
+        <v>-11.88815362946347</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.152919990052101</v>
       </c>
       <c r="E89">
-        <v>-25.01717634026585</v>
+        <v>-33.1480106647719</v>
       </c>
       <c r="F89">
-        <v>-4.62954592494987</v>
+        <v>-5.225360776557054</v>
       </c>
       <c r="G89">
-        <v>-8.827693321319908</v>
+        <v>-13.14603182311049</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.053404950734517</v>
       </c>
       <c r="E90">
-        <v>-26.02444934226597</v>
+        <v>-33.3286673425969</v>
       </c>
       <c r="F90">
-        <v>-4.51703375083203</v>
+        <v>-5.12291409475063</v>
       </c>
       <c r="G90">
-        <v>-9.579207022007703</v>
+        <v>-12.97234405139263</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.952767374819982</v>
       </c>
       <c r="E91">
-        <v>-27.29689619673325</v>
+        <v>-34.0162866855806</v>
       </c>
       <c r="F91">
-        <v>-4.110253168911096</v>
+        <v>-4.744246645745906</v>
       </c>
       <c r="G91">
-        <v>-8.6365854589744</v>
+        <v>-12.07822198050965</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.85187728143579</v>
       </c>
       <c r="E92">
-        <v>-28.00781680272341</v>
+        <v>-33.89716970528283</v>
       </c>
       <c r="F92">
-        <v>-5.234258270830523</v>
+        <v>-5.477631785405615</v>
       </c>
       <c r="G92">
-        <v>-9.20932970054155</v>
+        <v>-12.34148980397465</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.753348710155957</v>
       </c>
       <c r="E93">
-        <v>-29.29552914307055</v>
+        <v>-36.2986670205275</v>
       </c>
       <c r="F93">
-        <v>-4.751188364581366</v>
+        <v>-5.319937139669479</v>
       </c>
       <c r="G93">
-        <v>-9.509109530759174</v>
+        <v>-12.73188919723874</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.652984287360446</v>
       </c>
       <c r="E94">
-        <v>-30.14397044772564</v>
+        <v>-39.02351549381587</v>
       </c>
       <c r="F94">
-        <v>-4.549931533866809</v>
+        <v>-4.971780118844666</v>
       </c>
       <c r="G94">
-        <v>-9.565878765666596</v>
+        <v>-11.81524879559764</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.554363348139444</v>
       </c>
       <c r="E95">
-        <v>-32.85743660159573</v>
+        <v>-41.00376962839304</v>
       </c>
       <c r="F95">
-        <v>-5.056773099474103</v>
+        <v>-5.760323758754586</v>
       </c>
       <c r="G95">
-        <v>-9.235615432123364</v>
+        <v>-12.2638707532609</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.460188837284907</v>
       </c>
       <c r="E96">
-        <v>-33.60525521380039</v>
+        <v>-40.63027241342541</v>
       </c>
       <c r="F96">
-        <v>-4.906687008332681</v>
+        <v>-5.471346133553173</v>
       </c>
       <c r="G96">
-        <v>-8.823935852132834</v>
+        <v>-11.73276986403224</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.370955486722717</v>
       </c>
       <c r="E97">
-        <v>-36.4324426711881</v>
+        <v>-42.28437452878514</v>
       </c>
       <c r="F97">
-        <v>-5.60777493132464</v>
+        <v>-5.090525757668573</v>
       </c>
       <c r="G97">
-        <v>-9.484273818123562</v>
+        <v>-14.08092657285513</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.296209841930482</v>
       </c>
       <c r="E98">
-        <v>-37.88362160202711</v>
+        <v>-43.71470210105583</v>
       </c>
       <c r="F98">
-        <v>-5.421036067711547</v>
+        <v>-5.80613578959901</v>
       </c>
       <c r="G98">
-        <v>-9.129691217048842</v>
+        <v>-13.06549618177664</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.238514129028474</v>
       </c>
       <c r="E99">
-        <v>-38.99645106890903</v>
+        <v>-46.72412893793422</v>
       </c>
       <c r="F99">
-        <v>-5.530130397925436</v>
+        <v>-6.039049508978952</v>
       </c>
       <c r="G99">
-        <v>-10.16232320274939</v>
+        <v>-12.02534594715641</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.203295566171215</v>
       </c>
       <c r="E100">
-        <v>-43.46607529261271</v>
+        <v>-48.53898508785523</v>
       </c>
       <c r="F100">
-        <v>-5.747411167679747</v>
+        <v>-6.076099897803966</v>
       </c>
       <c r="G100">
-        <v>-10.05373068797022</v>
+        <v>-13.67715423088515</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.191967841834048</v>
       </c>
       <c r="E101">
-        <v>-45.03300881179879</v>
+        <v>-48.72925345176151</v>
       </c>
       <c r="F101">
-        <v>-5.94033462232214</v>
+        <v>-6.454025543799482</v>
       </c>
       <c r="G101">
-        <v>-10.11027811632651</v>
+        <v>-13.89847247654928</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.213975501073276</v>
       </c>
       <c r="E102">
-        <v>-47.37862928626281</v>
+        <v>-51.91259180443047</v>
       </c>
       <c r="F102">
-        <v>-5.868130806024524</v>
+        <v>-5.812297186341032</v>
       </c>
       <c r="G102">
-        <v>-11.68411146569603</v>
+        <v>-13.83786962990738</v>
       </c>
     </row>
   </sheetData>
